--- a/artfynd/A 49162-2024 artfynd.xlsx
+++ b/artfynd/A 49162-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121164230</v>
+        <v>121164130</v>
       </c>
       <c r="B2" t="n">
-        <v>5163</v>
+        <v>55950</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102185</v>
+        <v>206004</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579168</v>
+        <v>579445</v>
       </c>
       <c r="R2" t="n">
-        <v>6725273</v>
+        <v>6725180</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121164130</v>
+        <v>121164230</v>
       </c>
       <c r="B3" t="n">
-        <v>55950</v>
+        <v>5163</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206004</v>
+        <v>102185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579445</v>
+        <v>579168</v>
       </c>
       <c r="R3" t="n">
-        <v>6725180</v>
+        <v>6725273</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 49162-2024 artfynd.xlsx
+++ b/artfynd/A 49162-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121164130</v>
+        <v>121164844</v>
       </c>
       <c r="B2" t="n">
-        <v>55950</v>
+        <v>8421</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206004</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579445</v>
+        <v>579291</v>
       </c>
       <c r="R2" t="n">
-        <v>6725180</v>
+        <v>6725248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121164844</v>
+        <v>121164130</v>
       </c>
       <c r="B4" t="n">
-        <v>8421</v>
+        <v>55953</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>206004</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579291</v>
+        <v>579445</v>
       </c>
       <c r="R4" t="n">
-        <v>6725248</v>
+        <v>6725180</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 49162-2024 artfynd.xlsx
+++ b/artfynd/A 49162-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121164230</v>
+        <v>121164130</v>
       </c>
       <c r="B3" t="n">
-        <v>5163</v>
+        <v>55953</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102185</v>
+        <v>206004</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579168</v>
+        <v>579445</v>
       </c>
       <c r="R3" t="n">
-        <v>6725273</v>
+        <v>6725180</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121164130</v>
+        <v>121164230</v>
       </c>
       <c r="B4" t="n">
-        <v>55953</v>
+        <v>5163</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>206004</v>
+        <v>102185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579445</v>
+        <v>579168</v>
       </c>
       <c r="R4" t="n">
-        <v>6725180</v>
+        <v>6725273</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 49162-2024 artfynd.xlsx
+++ b/artfynd/A 49162-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121164844</v>
+        <v>121164130</v>
       </c>
       <c r="B2" t="n">
-        <v>8421</v>
+        <v>55953</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>206004</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579291</v>
+        <v>579445</v>
       </c>
       <c r="R2" t="n">
-        <v>6725248</v>
+        <v>6725180</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121164130</v>
+        <v>121164844</v>
       </c>
       <c r="B3" t="n">
-        <v>55953</v>
+        <v>8421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206004</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579445</v>
+        <v>579291</v>
       </c>
       <c r="R3" t="n">
-        <v>6725180</v>
+        <v>6725248</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 49162-2024 artfynd.xlsx
+++ b/artfynd/A 49162-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121164130</v>
       </c>
       <c r="B2" t="n">
-        <v>55953</v>
+        <v>55956</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121164844</v>
+        <v>121164230</v>
       </c>
       <c r="B3" t="n">
-        <v>8421</v>
+        <v>5166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>102185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579291</v>
+        <v>579168</v>
       </c>
       <c r="R3" t="n">
-        <v>6725248</v>
+        <v>6725273</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121164230</v>
+        <v>121164844</v>
       </c>
       <c r="B4" t="n">
-        <v>5163</v>
+        <v>8424</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102185</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579168</v>
+        <v>579291</v>
       </c>
       <c r="R4" t="n">
-        <v>6725273</v>
+        <v>6725248</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 49162-2024 artfynd.xlsx
+++ b/artfynd/A 49162-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121164130</v>
+        <v>121164844</v>
       </c>
       <c r="B2" t="n">
-        <v>55956</v>
+        <v>8424</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206004</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579445</v>
+        <v>579291</v>
       </c>
       <c r="R2" t="n">
-        <v>6725180</v>
+        <v>6725248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121164844</v>
+        <v>121164130</v>
       </c>
       <c r="B4" t="n">
-        <v>8424</v>
+        <v>55956</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>206004</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579291</v>
+        <v>579445</v>
       </c>
       <c r="R4" t="n">
-        <v>6725248</v>
+        <v>6725180</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 49162-2024 artfynd.xlsx
+++ b/artfynd/A 49162-2024 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>121164130</v>
       </c>
       <c r="B4" t="n">
-        <v>55956</v>
+        <v>55957</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
